--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486295_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486295_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9558</v>
+        <v>11.5099</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8573</v>
+        <v>7.5964</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0985</v>
+        <v>3.9135</v>
       </c>
       <c r="G2" t="n">
         <v>5.0079</v>
@@ -610,13 +610,13 @@
         <v>4.3501</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2502</v>
+        <v>1.8043</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8977000000000001</v>
+        <v>1.6367</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3526</v>
+        <v>0.1676</v>
       </c>
       <c r="V2" t="n">
         <v>0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.654</v>
+        <v>11.317</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7651</v>
+        <v>9.2432</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8889</v>
+        <v>2.0739</v>
       </c>
       <c r="G3" t="n">
         <v>4.0988</v>
@@ -688,13 +688,13 @@
         <v>3.9151</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2072</v>
+        <v>1.4559</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2211</v>
+        <v>1.6992</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4283</v>
+        <v>-0.2434</v>
       </c>
       <c r="V3" t="n">
         <v>2.0647</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8.6431</v>
+        <v>7.2665</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5282</v>
+        <v>4.3673</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1149</v>
+        <v>2.8991</v>
       </c>
       <c r="G4" t="n">
         <v>4.2309</v>
@@ -766,13 +766,13 @@
         <v>3.4801</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4769</v>
+        <v>2.1003</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1893</v>
+        <v>2.0285</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2876</v>
+        <v>0.0718</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3698</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.434</v>
+        <v>3.8474</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8921</v>
+        <v>2.7371</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5419</v>
+        <v>1.1104</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7915</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3358</v>
+        <v>0.7493</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4026</v>
+        <v>0.2476</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9332</v>
+        <v>0.5017</v>
       </c>
       <c r="V5" t="n">
         <v>4.3247</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5569</v>
+        <v>2.9888</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7953</v>
+        <v>0.597</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7616</v>
+        <v>2.3918</v>
       </c>
       <c r="G6" t="n">
         <v>0.5149</v>
@@ -922,13 +922,13 @@
         <v>3.0451</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2145</v>
+        <v>1.6463</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3447</v>
+        <v>1.1464</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8698</v>
+        <v>0.4999</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2836</v>
+        <v>1.7182</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3061</v>
+        <v>0.5626</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0224</v>
+        <v>1.1557</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6745</v>
+        <v>0.9115</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006</v>
+        <v>-0.4472</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6805</v>
+        <v>1.3587</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1246</v>
+        <v>1.3793</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.3832</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7451</v>
+        <v>0.9961</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.4679</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.8304</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0645</v>
+        <v>0.3626</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5024</v>
+        <v>0.307</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8673</v>
+        <v>0.4458</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3648</v>
+        <v>-0.1388</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5857</v>
+        <v>0.9347</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7809</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
         <v>-0.1952</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4215</v>
+        <v>1.6188</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4508</v>
+        <v>1.5179</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9707</v>
+        <v>0.1009</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9115</v>
+        <v>-0.6745</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4472</v>
+        <v>0.006</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3587</v>
+        <v>-0.6805</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3793</v>
+        <v>-0.1246</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3832</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9961</v>
+        <v>-0.7451</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4679</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8304</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3626</v>
+        <v>0.0645</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0103</v>
+        <v>0.8376</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3341</v>
+        <v>1.0791</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3237</v>
+        <v>-0.2415</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9347</v>
+        <v>0.5857</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0.7809</v>
       </c>
       <c r="X8" t="n">
         <v>-0.1952</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.436</v>
+        <v>1.2491</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4535</v>
+        <v>-0.6712</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8895</v>
+        <v>1.9203</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8314</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2775</v>
+        <v>0.5357</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1935</v>
+        <v>0.5888</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0532</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1952</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>P. FIGUERAS LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.88</v>
+        <v>-0.6817</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2463</v>
+        <v>-1.7824</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.1007</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7587</v>
+        <v>-1.0873</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.18</v>
+        <v>-1.2499</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9388</v>
+        <v>0.1626</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4577</v>
+        <v>-0.1859</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4166</v>
+        <v>-1.049</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8742</v>
+        <v>0.863</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6989</v>
+        <v>-0.9013</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7635</v>
+        <v>-0.2009</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0645</v>
+        <v>-0.7004</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6218</v>
+        <v>0.6453</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6886</v>
+        <v>0.3833</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0668</v>
+        <v>0.262</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9554</v>
+        <v>0.1952</v>
       </c>
       <c r="W10" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. FIGUERAS LOPEZ</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8476</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7017</v>
+        <v>-0.3581</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8541</v>
+        <v>-0.5103</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0873</v>
+        <v>0.7587</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2499</v>
+        <v>-1.18</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1626</v>
+        <v>1.9388</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1859</v>
+        <v>1.4577</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.049</v>
+        <v>-0.4166</v>
       </c>
       <c r="L11" t="n">
-        <v>0.863</v>
+        <v>1.8742</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9013</v>
+        <v>-0.6989</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2009</v>
+        <v>-0.7635</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7004</v>
+        <v>0.0645</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5206</v>
+        <v>0.6333</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.536</v>
+        <v>0.5768</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0154</v>
+        <v>0.0565</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1952</v>
+        <v>-0.9554</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.355499999999999</v>
+        <v>-7.9788</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.594</v>
+        <v>-5.5255</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7615</v>
+        <v>-2.4533</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2769</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3184</v>
+        <v>0.0583</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0769</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2415</v>
+        <v>0.0667</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4552</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.3018</v>
+        <v>31.9868</v>
       </c>
       <c r="E13" t="n">
-        <v>17.5994</v>
+        <v>18.2843</v>
       </c>
       <c r="F13" t="n">
-        <v>13.7026</v>
+        <v>13.7027</v>
       </c>
       <c r="G13" t="n">
-        <v>7.861099999999998</v>
+        <v>7.8611</v>
       </c>
       <c r="H13" t="n">
         <v>-1.9006</v>
@@ -1468,13 +1468,13 @@
         <v>23.9257</v>
       </c>
       <c r="S13" t="n">
-        <v>10.0882</v>
+        <v>10.7733</v>
       </c>
       <c r="T13" t="n">
-        <v>9.138999999999999</v>
+        <v>9.8238</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9495000000000002</v>
+        <v>0.9493</v>
       </c>
       <c r="V13" t="n">
         <v>3.5644</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5062</v>
+        <v>1.5049</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7243</v>
+        <v>2.389</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2181</v>
+        <v>-0.8841</v>
       </c>
       <c r="G14" t="n">
         <v>2.7989</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0327</v>
+        <v>-1.0341</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3341</v>
+        <v>-0.0012</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3668</v>
+        <v>-1.0329</v>
       </c>
       <c r="V14" t="n">
         <v>-1.13</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. KELLY</t>
+          <t>S. THOMAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1289</v>
+        <v>1.4564</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7857</v>
+        <v>3.076</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3433</v>
+        <v>-1.6196</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5918</v>
+        <v>1.6855</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5432</v>
+        <v>3.7103</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0486</v>
+        <v>-2.0248</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1355</v>
+        <v>3.1456</v>
       </c>
       <c r="K15" t="n">
-        <v>3.58</v>
+        <v>3.8141</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5554</v>
+        <v>-0.6686</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5436</v>
+        <v>-1.4601</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0368</v>
+        <v>-0.1038</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5068</v>
+        <v>-1.3563</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.3926</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0703</v>
+        <v>-2.0318</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8051</v>
+        <v>-0.3497</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-1.6821</v>
       </c>
       <c r="V15" t="n">
+        <v>2.4552</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.4552</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.1952</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. THOMAS</t>
+          <t>A. KELLY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8539</v>
+        <v>0.8258</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7407</v>
+        <v>0.3387</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8868</v>
+        <v>0.4872</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6855</v>
+        <v>3.5918</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7103</v>
+        <v>3.5432</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0248</v>
+        <v>0.0486</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1456</v>
+        <v>4.1355</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8141</v>
+        <v>3.58</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6686</v>
+        <v>0.5554</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4601</v>
+        <v>-0.5436</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1038</v>
+        <v>-0.0368</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3563</v>
+        <v>-0.5068</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6525</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-4.3501</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.6342</v>
+        <v>-0.3734</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.3581</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.9493</v>
+        <v>-0.7315</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4552</v>
+        <v>0.1952</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0285</v>
+        <v>-1.8049</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2135</v>
+        <v>1.121</v>
       </c>
       <c r="G17" t="n">
         <v>0.591</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1662</v>
+        <v>-0.0352</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2448</v>
+        <v>0.1523</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3698</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7425</v>
+        <v>-1.2146</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0542</v>
+        <v>0.5046</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6883</v>
+        <v>-1.7191</v>
       </c>
       <c r="G18" t="n">
         <v>0.8893</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2621</v>
+        <v>0.2659</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.548</v>
+        <v>0.0108</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2859</v>
+        <v>0.2551</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4997</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5563</v>
+        <v>-2.0476</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.584</v>
+        <v>-0.137</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9722</v>
+        <v>-1.9106</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1574</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.139</v>
+        <v>-0.6303</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4795</v>
+        <v>-0.0324</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6595</v>
+        <v>-0.5979</v>
       </c>
       <c r="V19" t="n">
         <v>-1.13</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0892</v>
+        <v>-3.8375</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8157</v>
+        <v>-4.2627</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2736</v>
+        <v>0.4251</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1559</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4983</v>
+        <v>-0.2466</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8051</v>
+        <v>0.3581</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3035</v>
+        <v>-0.6048</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9375</v>
+        <v>-5.1583</v>
       </c>
       <c r="E21" t="n">
         <v>-1.4784</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.459</v>
+        <v>-3.6799</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6235000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7283</v>
+        <v>-1.9492</v>
       </c>
       <c r="T21" t="n">
         <v>-0.7534999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9748</v>
+        <v>-1.1957</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7156</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1492</v>
+        <v>-6.2417</v>
       </c>
       <c r="E22" t="n">
         <v>-2.6432</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.506</v>
+        <v>-3.5985</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0559</v>
@@ -2170,13 +2170,13 @@
         <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2658</v>
+        <v>-1.3582</v>
       </c>
       <c r="T22" t="n">
         <v>-0.274</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9918</v>
+        <v>-1.0842</v>
       </c>
       <c r="V22" t="n">
         <v>1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.7185</v>
+        <v>-7.0859</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5153</v>
+        <v>-3.1859</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2032</v>
+        <v>-3.9001</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4169</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3647</v>
+        <v>-0.7321</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8051</v>
+        <v>0.1346</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1699</v>
+        <v>-0.8667</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1093</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.7827</v>
+        <v>-7.3292</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8339</v>
+        <v>-6.4986</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9488</v>
+        <v>-0.8306</v>
       </c>
       <c r="G24" t="n">
         <v>-6.0083</v>
@@ -2326,13 +2326,13 @@
         <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9266</v>
+        <v>-0.4732</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.548</v>
+        <v>-0.2127</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3787</v>
+        <v>-0.2605</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1952</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.3019</v>
+        <v>-29.8117</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.7025</v>
+        <v>-13.7024</v>
       </c>
       <c r="F25" t="n">
-        <v>-17.5992</v>
+        <v>-16.1092</v>
       </c>
       <c r="G25" t="n">
         <v>-7.861399999999999</v>
@@ -2404,13 +2404,13 @@
         <v>14.1377</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.0882</v>
+        <v>-8.5982</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9496000000000001</v>
+        <v>-0.9493999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.139100000000001</v>
+        <v>-7.6489</v>
       </c>
       <c r="V25" t="n">
         <v>-3.5644</v>
